--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-familymemberhistory.xlsx
@@ -453,13 +453,13 @@
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>FamilyMemberHistory.extension:BirthOrderLabel</t>
-  </si>
-  <si>
-    <t>BirthOrderLabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_FamilyMemberHistory_BirthOrderLabel}
+    <t>FamilyMemberHistory.extension:BirthOrder</t>
+  </si>
+  <si>
+    <t>BirthOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_FamilyMemberHistory_BirthOrder}
 </t>
   </si>
   <si>
@@ -1312,7 +1312,7 @@
   <cols>
     <col min="1" max="1" width="42.19140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.19140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.40234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-familymemberhistory.xlsx
@@ -262,11 +262,10 @@
 </t>
   </si>
   <si>
-    <t>Information about patient's relatives, relevant for patient. 患者に関連する家族の情報（家族歴）</t>
-  </si>
-  <si>
-    <t>Significant health conditions for a person related to the patient relevant in the context of care for the patient.  
-患者の診療に関連する、患者家族の重要な健康状態に関する情報。</t>
+    <t>患者の家族の、患者の診療に関連する情報（家族歴）</t>
+  </si>
+  <si>
+    <t>患者の家族の、患者の診療に関連する重要な健康状態に関する情報。</t>
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-familymemberhistory.xlsx
@@ -465,7 +465,7 @@
     <t>出生順（呼称）</t>
   </si>
   <si>
-    <t>FamilyMemberHistoryにおいて、対象となる家族構成員について、家族内で用いられる出生順に基づく呼称を表現する。これは、患者との続柄そのものを置き換えるものではなく、FamilyMemberHistory.relationshipで表現される続柄を補足する情報である。日常の臨床では家族の氏名まで聴取されずに、長女、二男などの呼称で記述され、関係者全員の生年月日や年齢も聴取できない場合が多いことを想定している。</t>
+    <t>FamilyMemberHistoryにおいて、対象となる家族構成員について、家族内で用いられる出生順に基づく呼称を表現する。これは、患者との続柄そのものを置き換えるものではなく、FamilyMemberHistory.relationshipで表現される続柄を補足する情報である。日常の臨床では家族の氏名まで聴取されずに、長女、次男などの呼称で記述され、関係者全員の生年月日や年齢も聴取できない場合が多いことを想定している。</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
